--- a/publications.xlsx
+++ b/publications.xlsx
@@ -337,7 +337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.50390625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.84" customWidth="1" style="2" min="1" max="1"/>
@@ -403,82 +403,82 @@
           <t>Year</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Paper Link</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Preprint</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>ShareIt</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Supplemental Information</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Highly Cited</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Hot Paper</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>Awards</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Media Coverage</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Invited Presentation</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="2" t="inlineStr">
         <is>
           <t>Categories</t>
         </is>
@@ -525,12 +525,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fnhum.2025.1686657</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>10.3389/fnhum.2025.1686657</t>
         </is>
@@ -587,12 +587,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1371/journal.pone.0328318</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>10.1371/journal.pone.0328318</t>
         </is>
@@ -649,12 +649,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1515/revneuro-2025-0094</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>10.1515/revneuro-2025-0094</t>
         </is>
@@ -701,12 +701,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.3389/fpsyg.2026.1746459</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>10.3389/fpsyg.2026.1746459</t>
         </is>
@@ -753,12 +753,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.neuroimage.2026.121759</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.neuroimage.2026.121759</t>
         </is>
@@ -805,12 +805,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.64898/2026.01.31.703018</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>10.64898/2026.01.31.703018</t>
         </is>
@@ -867,12 +867,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1136/bmjopen-2025-103595</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>10.1136/bmjopen-2025-103595</t>
         </is>
@@ -919,12 +919,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.64898/2026.03.09.710521</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>10.64898/2026.03.09.710521</t>
         </is>
@@ -971,12 +971,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1017/s0007114526106989</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>10.1017/s0007114526106989</t>
         </is>
@@ -1023,12 +1023,12 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.neuroimage.2026.121885</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.neuroimage.2026.121885</t>
         </is>
@@ -1075,14 +1075,118 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/j.neuroimage.2026.121933</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10.1016/j.neuroimage.2026.121933</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Preprint</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Gastaldon S,Romeo F,Barattieri di San Pietro C,Chumakova N,D'Imperio D,Lago S,Nordio S,Parrotta I,Rigoni M,Bambini V,Arcara G</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Challenging the right-hemisphere assumption in post-stroke pragmatics: largely comparable impairment profiles across lesion sides</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>bioRxiv</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.64898/2026.08.06.742887</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10.64898/2026.08.06.742887</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Peer-reviewed Journal Paper</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Turrini S,Amadori A,Zago S,Arcara G,Avenanti A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Timing and circuit engagement shape state-dependent plasticity in the ventral premotor-motor pathway</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Clinical Neurophysiology</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2112352</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2026 Nov</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.clinph.2026.2112352</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.clinph.2026.2112352</t>
         </is>
       </c>
     </row>
